--- a/data-manipulation-scripts/sheets-cleanup/sheets/MANGUEIRA COMBUSTIVEL 11_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/MANGUEIRA COMBUSTIVEL 11_02.xlsx
@@ -360,7 +360,9 @@
       <c r="C3" s="2">
         <v>1.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>80.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -372,7 +374,9 @@
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>80.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3"/>
